--- a/data_extactor/batch_10_fa/batch_0023_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0023_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ESRI ArcGIS software | ESRI ArcView | Forest Metrix | Forest vegetation simulators | Forest yield software | Fountains Forestry TwoDog | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | IBM Notes | نرم‌افزار نقشه برداری | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SMART service management and route tracking software | Trimble CENGEA | نرم‌افزار مرورگر وب | نرم‌افزار برنامه‌ریزی کاری</t>
+          <t>نرم‌افزار ESRI ArcGIS | ESRI ArcView | Forest Metrix | Forest vegetation simulators | Forest yield software | Fountains Forestry TwoDog | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | IBM Notes | نرم‌افزار نقشه‌برداری | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SMART service management and route tracking software | Trimble CENGEA | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | سخن‌گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | امور اداری و مدیریت | زیست‌شناسی | قوانین و مقررات دولتی | ریاضیات | جغرافیا | امنیت و ایمنی عمومی | آموزش و تربیت | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | زیست‌شناسی | قانون و دولت | ریاضیات | جغرافیا | ایمنی و امنیت عمومی | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | انعطاف‌پذیری در دسته‌بندی | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری در بستار | خلاقیت | بینایی دور | قدرت تنه | تجسم | روانی ایده‌ها | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | اصالت | بینایی دور | قدرت تنه | تجسم | روانی ایده‌ها | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت دقیق بودن یا صحت بالا | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم | فضای بسته، با دمای کنترل‌شده</t>
+          <t>ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Agricultural Engineers | Brownfield Redevelopment Specialists and Site Managers | Chief Sustainability Officers | Conservation Scientists | Environmental Engineers | Environmental Restoration Planners | Environmental Science and Protection Technicians, Including Health | Environmental Scientists and Specialists, Including Health | Fallers | First-Line Supervisors of Farming, Fishing, and Forestry Workers | Forest Fire Inspectors and Prevention Specialists | Forest and Conservation Technicians | Forest and Conservation Workers | Hydrologists | Industrial Ecologists | Precision Agriculture Technicians | Range Managers | Soil and Plant Scientists | Water Resource Specialists | Zoologists and Wildlife Biologists</t>
+          <t>مهندسان کشاورزی | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | دانشمندان حفاظت | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | قطع‌کنندگان درختان | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | آب‌شناسان | بوم‌شناسان صنعتی | تکنسین‌های کشاورزی دقیق | مدیران مراتع | دانشمندان خاک و گیاه | متخصصان منابع آب | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Centers for Disease Control and Prevention CDC WONDER | Centers for Disease Control and Prevention Epi Info | Circle Systems Stat/Transfer | Cytel Egret | نرم‌افزار تجسم داده‌ها | نرم‌افزار پایگاه داده | Disease Mapping and Analysis Program DMAP | ESRI ArcGIS software | ESRI ArcInfo | ESRI ArcView | EpiData Analysis | Epicenter Software Epilog | Esri ArcGIS | Expert Health Data Programming Vitalnet | Facebook | GeoDa | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | HiroSoft EPICURE | IBM SPSS Statistics | Meta-analysis with interactive explanations MIX | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | National Institute for Occupational Safety and Health NIOSH Life Table Analysis System | Pan American Health Organization SIGEpi | Python | R | RTI International SUDAAN | SAS | SaTScan | نرم‌افزار تشخیص سیگنال | StataCorp Stata | نرم‌افزار پردازش آماری | نرم‌افزار آماری | Structured query language SQL | Tableau | TerraSeer ClusterSeer | نرم‌افزار مرورگر وب | World Health Organization HealthMapper</t>
+          <t>Centers for Disease Control and Prevention CDC WONDER | Centers for Disease Control and Prevention Epi Info | Circle Systems Stat/Transfer | Cytel Egret | نرم‌افزار تجسم داده | نرم‌افزار پایگاه داده | Disease Mapping and Analysis Program DMAP | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | ESRI ArcView | EpiData Analysis | Epicenter Software Epilog | Esri ArcGIS | Expert Health Data Programming Vitalnet | Facebook | GeoDa | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | HiroSoft EPICURE | IBM SPSS Statistics | Meta-analysis with interactive explanations MIX | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | National Institute for Occupational Safety and Health NIOSH Life Table Analysis System | Pan American Health Organization SIGEpi | Python | R | RTI International SUDAAN | SAS | SaTScan | نرم‌افزار تشخیص سیگنال | StataCorp Stata | نرم‌افزار پردازش آماری | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | Tableau | TerraSeer ClusterSeer | نرم‌افزار مرورگر وب | World Health Organization HealthMapper</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن‌گفتن | علوم تجربی | یادگیری فعال | ریاضیات | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | علوم | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ریاضیات | زیست‌شناسی | زبان انگلیسی | پزشکی و دندانپزشکی | کامپیوتر و الکترونیک | ارتباطات و رسانه | آموزش و تربیت | جامعه‌شناسی و انسان‌شناسی | امور اداری و مدیریت</t>
+          <t>ریاضیات | زیست‌شناسی | زبان انگلیسی | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | ارتباطات و رسانه | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری در دسته‌بندی | وضوح گفتار | روانی ایده‌ها | خلاقیت | بینایی نزدیک | سازماندهی اطلاعات | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری در بستار | سهولت کار با اعداد | توجه انتخابی | تجسم | سرعت ادراکی | سرعت بستار</t>
+          <t>درک شفاهی | درک کتبی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | روانی ایده‌ها | اصالت | بینایی نزدیک | ترتیب‌دهی اطلاعات | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی | توجه انتخابی | تجسم | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | فضای بسته، با دمای کنترل‌شده | اهمیت دقیق بودن یا صحت بالا | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان به صورت نشسته | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Cardiologists | Clinical Neuropsychologists | Clinical Nurse Specialists | Clinical Research Coordinators | Emergency Medicine Physicians | General Internal Medicine Physicians | Genetic Counselors | Geneticists | Health Education Specialists | Health Informatics Specialists | Health Information Technologists and Medical Registrars | Health Specialties Teachers, Postsecondary | Medical Scientists, Except Epidemiologists | Microbiologists | Neuropsychologists | Nurse Practitioners | Pediatric Surgeons | Physicians, Pathologists | Preventive Medicine Physicians</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان قلب | عصب‌روان‌شناسان بالینی | متخصصان پرستاری بالینی | هماهنگ‌کنندگان تحقیقات بالینی | پزشکان طب اورژانس | پزشکان داخلی عمومی | مشاوران ژنتیک | ژنتیک‌دان‌ها | متخصصان آموزش بهداشت | متخصصان انفورماتیک سلامت | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | استادان تخصص‌های بهداشتی، پس از متوسطه | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | میکروبیولوژیست‌ها | عصب‌روان‌شناسان | پرستاران متخصص | جراحان کودکان | پزشکان، آسیب‌شناسان | پزشکان طب پیشگیری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | BioArray Software Environment BASE | نرم‌افزار پایگاه داده | ESRI ArcGIS software | FileMaker Pro | IBM Notes | IBM SPSS Statistics | نرم‌افزار محیط توسعه یکپارچه IDE | LexisNexis | Linux | Medical Scientists HybridAI | Medical Scientists MediSave | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Visual Basic | Microsoft Word | Minitab | National Instruments LabVIEW | PerkinElmer TurboMass | Python | R | SAS | StataCorp Stata | نرم‌افزار آماری | The MathWorks MATLAB | Thermo ToxLab | Triple G ULTRA Laboratory Information System | UNIX | Waters Empower 2 | Waters MassLynx | Waters Millennium32 | Waters Q-DIS/QM LIMS</t>
+          <t>Adobe Photoshop | BioArray Software Environment BASE | نرم‌افزار پایگاه داده | نرم‌افزار ESRI ArcGIS | FileMaker Pro | IBM Notes | IBM SPSS Statistics | نرم‌افزار محیط توسعه یکپارچه IDE | LexisNexis | Linux | Medical Scientists HybridAI | Medical Scientists MediSave | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Visual Basic | Microsoft Word | Minitab | National Instruments LabVIEW | PerkinElmer TurboMass | Python | R | SAS | StataCorp Stata | نرم‌افزار آماری | The MathWorks MATLAB | Thermo ToxLab | Triple G ULTRA Laboratory Information System | UNIX | Waters Empower 2 | Waters MassLynx | Waters Millennium32 | Waters Q-DIS/QM LIMS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نگارش | علوم تجربی | یادگیری فعال | سخن‌گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | ریاضیات | نظارت | استراتژی‌های یادگیری</t>
+          <t>نگارش | علوم | یادگیری فعال | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | پزشکی و دندانپزشکی | شیمی | ریاضیات</t>
+          <t>زیست‌شناسی | زبان انگلیسی | پزشکی و دندان‌پزشکی | شیمی | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | سازماندهی اطلاعات | انعطاف‌پذیری در دسته‌بندی | درک شفاهی | درک کتبی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | روانی ایده‌ها | خلاقیت | انعطاف‌پذیری در بستار | سهولت کار با اعداد | توجه انتخابی | سرعت بستار | به خاطرسپاری | سرعت ادراکی</t>
+          <t>بیان شفاهی | بیان کتبی | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک شفاهی | درک کتبی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | توانایی عددی | توجه انتخابی | سرعت بستار | حفظ کردن | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فضای بسته، با دمای کنترل‌شده | ارتباط با دیگران | اهمیت دقیق بودن یا صحت بالا | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سطح رقابت | اهمیت تکرار وظایف مشابه | مکالمات تلفنی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارگران | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سطح رقابت | اهمیت تکرار وظایف یکسان | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Biochemists and Biophysicists | Bioengineers and Biomedical Engineers | Bioinformatics Scientists | Biological Technicians | Cardiologists | Clinical Neuropsychologists | Clinical Research Coordinators | Cytogenetic Technologists | Epidemiologists | Geneticists | Histotechnologists | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Microbiologists | Molecular and Cellular Biologists | Pediatric Surgeons | Physicians, Pathologists | Preventive Medicine Physicians | Radiologists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های زیستی | متخصصان قلب | عصب‌روان‌شناسان بالینی | هماهنگ‌کنندگان تحقیقات بالینی | تکنولوژیست‌های سیتوژنتیک | اپیدمیولوژیست‌ها | ژنتیک‌دان‌ها | هیستوتکنولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | جراحان کودکان | پزشکان، آسیب‌شناسان | پزشکان طب پیشگیری | رادیولوژیست‌ها</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Laboratory information management system LIMS | Microsoft Excel | Microsoft Word | IBM SPSS Statistics | SAS | R | Python | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Microsoft PowerPoint | Minitab | نرم‌افزار مرورگر وب</t>
+          <t>سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Microsoft Excel | Microsoft Word | IBM SPSS Statistics | SAS | R | Python | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Microsoft PowerPoint | Minitab | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن‌گفتن | گوش دادن فعال | علوم تجربی | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | پزشکی و دندانپزشکی | کامپیوتر و الکترونیک | آموزش و تربیت | امور اداری و مدیریت | فیزیک</t>
+          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | آموزش و پرورش | مدیریت و اداره | فیزیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | اشتراک زمانی | تجسم | به خاطرسپاری | استدلال ریاضی | سهولت کار با اعداد | سرعت ادراکی | انعطاف‌پذیری در بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | فضای بسته، با دمای کنترل‌شده | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق بودن یا صحت بالا | فشار زمانی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامد خطا | اهمیت تکرار وظایف مشابه</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامد خطا | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Biologists | Microbiologists | Biochemists and Biophysicists | Molecular and Cellular Biologists | Geneticists | Bioinformatics Scientists | Medical Scientists, Except Epidemiologists | Epidemiologists | Zoologists and Wildlife Biologists | Animal Scientists | Soil and Plant Scientists | Food Scientists and Technologists | Conservation Scientists | Foresters | Environmental Scientists and Specialists, Including Health | Biological Technicians | Natural Sciences Managers | Biological Science Teachers, Postsecondary | Health Specialties Teachers, Postsecondary | Clinical Research Coordinators</t>
+          <t>زیست‌شناسان | میکروبیولوژیست‌ها | بیوشیمی‌دانان و بیوفیزیک‌دانان | زیست‌شناسان مولکولی و سلولی | ژنتیک‌دان‌ها | دانشمندان بیوانفورماتیک | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | اپیدمیولوژیست‌ها | جانورشناسان و زیست‌شناسان حیات وحش | دانشمندان علوم دامی | دانشمندان خاک و گیاه | دانشمندان و تکنولوژیست‌های علوم غذایی | دانشمندان حفاظت | جنگل‌بانان | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تکنسین‌های زیستی | مدیران علوم طبیعی | مدرسان علوم زیستی، پس از متوسطه | استادان تخصص‌های بهداشتی، پس از متوسطه | هماهنگ‌کنندگان تحقیقات بالینی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Abstraction plus reference plus synthesis A++ | Adaptive optics AO simulation software | Analyze | Apache Hadoop | Astronomical Image Processing System AIPS | Astronomical Image Processing for Windows AIP4WIN | Astronomical information processing system AIPS++ | Avis Fits Viewer | C | C++ | نرم‌افزار کاهش داده | Diffraction Limited MaxIm DL | European Southern Observatory Munich Image Data Analysis System ESO-MIDAS | Formula translation/translator FORTRAN | Fortran | IBM SPSS Statistics | IRIS | Interface definition language IDL | Linux | MSB Software Astroart | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Multipurpose Interactive Image Processing System MIIPS | National Instruments LabVIEW | Oracle Java | Python | R | SAS | Software Bisque CCDSoft | ابزارهای توسعه نرم‌افزار | پایگاه‌های داده طیف‌سنجی | Starcal | Structured query language SQL | The MathWorks MATLAB | Visual Numerics PV-WAVE | نرم‌افزار مرورگر وب</t>
+          <t>Abstraction plus reference plus synthesis A++ | Adaptive optics AO simulation software | Analyze | Apache Hadoop | Astronomical Image Processing System AIPS | Astronomical Image Processing for Windows AIP4WIN | Astronomical information processing system AIPS++ | Avis Fits Viewer | C | C++ | نرم‌افزار کاهش داده | Diffraction Limited MaxIm DL | European Southern Observatory Munich Image Data Analysis System ESO-MIDAS | Formula translation/translator FORTRAN | Fortran | IBM SPSS Statistics | IRIS | زبان تعریف رابط IDL | Linux | MSB Software Astroart | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Multipurpose Interactive Image Processing System MIIPS | National Instruments LabVIEW | Oracle Java | Python | R | SAS | Software Bisque CCDSoft | ابزارهای توسعه نرم‌افزار | پایگاه‌های داده طیف‌سنجی | Starcal | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | Visual Numerics PV-WAVE | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم تجربی | نگارش | ریاضیات | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | سخن‌گفتن | استراتژی‌های یادگیری | نظارت</t>
+          <t>درک مطلب | علوم | نگارش | ریاضیات | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | سخن گفتن | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>فیزیک | ریاضیات | کامپیوتر و الکترونیک | زبان انگلیسی | آموزش و تربیت | مهندسی و فناوری | شیمی</t>
+          <t>فیزیک | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | مهندسی و فناوری | شیمی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | سهولت کار با اعداد | وضوح گفتار | سازماندهی اطلاعات | انعطاف‌پذیری در بستار | بینایی نزدیک | بینایی دور | روانی ایده‌ها | خلاقیت | حساسیت به مسئله | انعطاف‌پذیری در دسته‌بندی | توجه انتخابی | تشخیص گفتار | سرعت ادراکی | تشخیص رنگ‌های بصری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | توانایی عددی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی نزدیک | بینایی دور | روانی ایده‌ها | اصالت | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تشخیص گفتار | سرعت ادراکی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت نشسته | اهمیت دقیق بودن یا صحت بالا | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | فضای بسته، با دمای کنترل‌شده | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Atmospheric and Space Scientists | Atmospheric, Earth, Marine, and Space Sciences Teachers, Postsecondary | Biochemists and Biophysicists | Bioinformatics Scientists | Biologists | Chemists | Computer and Information Research Scientists | Data Scientists | Engineering Teachers, Postsecondary | Environmental Science Teachers, Postsecondary | Geoscientists, Except Hydrologists and Geographers | Hydrologists | Mathematical Science Teachers, Postsecondary | Mathematicians | Molecular and Cellular Biologists | Nanosystems Engineers | Nanotechnology Engineering Technologists and Technicians | Physicists | Physics Teachers, Postsecondary | Statisticians</t>
+          <t>دانشمندان علوم جوی و فضایی | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | بیوشیمی‌دانان و بیوفیزیک‌دانان | دانشمندان بیوانفورماتیک | زیست‌شناسان | شیمی‌دانان | دانشمندان تحقیقات کامپیوتر و اطلاعات | دانشمندان داده | مدرسان مهندسی، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | آب‌شناسان | مدرسان علوم ریاضی، پس از متوسطه | ریاضی‌دانان | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | فیزیکدانان | مدرسان فیزیک، پس از متوسطه | آمارشناسان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Adobe Audition | Adobe Photoshop | Amazon Web Services AWS software | نرم‌افزار Ansible | Aptech Systems GAUSS | Autodesk AutoCAD | C | C++ | CERN Physics Analysis Workstation PAW | CERN ROOT | COMSOL Multiphysics | Canu | Criss Software XRF11 | نرم‌افزار کاربردی پایگاه داده | نرم‌افزار مدل‌سازی دوز | Eclipse IDE | سیستم برنامه‌ریزی منابع سازمانی ERP | Experimental Physics and Industrial Control System EPICS | زبان نشانه گذاری گسترش پذیر XML | Formula translation/translator FORTRAN | GNU Image Manipulation Program GIMP | GNU Octave | Git | Gnuplot | JavaScript | Lenox Softworks VideoPoint | Linux | Maplesoft Maple | Mathsoft Mathcad | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Visual J++ | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | MySQL | National Instruments LabVIEW | OpenStack | Oracle Database | Oracle Java | OriginLab Origin | Pascal | Perl | Ploticus | Puppet | Python | REDUCE | RSI interactive data language IDL software | نرم‌افزار محاسبه دوز تابش | RibbonSoft QCad | SQLite | SciGraphica | SciLab | Scribus | ابزارهای توسعه نرم‌افزار | Spectral Dynamics STAR | نرم‌افزار طیف‌سنجی | نرم‌افزار آماری | Structured query language SQL | Sun Microsystems Java | Synergy Software KaleidaGraph | Systat Software SigmaPlot | The MathWorks MATLAB | UNIX | VMware | Vector Fields OPERA-3d | نرم‌افزار تحلیل ویدیو | Wolfram Research Mathematica | Xfig | xv</t>
+          <t>Adobe Audition | Adobe Photoshop | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Aptech Systems GAUSS | Autodesk AutoCAD | C | C++ | CERN Physics Analysis Workstation PAW | CERN ROOT | COMSOL Multiphysics | Canu | Criss Software XRF11 | نرم‌افزار کاربردی پایگاه داده | نرم‌افزار مدل‌سازی دوز | Eclipse IDE | سیستم برنامه‌ریزی منابع سازمانی ERP | Experimental Physics and Industrial Control System EPICS | زبان نشانه‌گذاری توسعه‌پذیر XML | Formula translation/translator FORTRAN | برنامه دستکاری تصویر گنو GIMP | GNU Octave | Git | Gnuplot | JavaScript | Lenox Softworks VideoPoint | Linux | Maplesoft Maple | Mathsoft Mathcad | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Visual J++ | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | MySQL | National Instruments LabVIEW | OpenStack | Oracle Database | Oracle Java | OriginLab Origin | Pascal | Perl | Ploticus | Puppet | Python | REDUCE | RSI interactive data language IDL software | نرم‌افزار محاسبه دوز تابش | RibbonSoft QCad | SQLite | SciGraphica | SciLab | Scribus | ابزارهای توسعه نرم‌افزار | Spectral Dynamics STAR | نرم‌افزار طیف‌سنجی | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java | Synergy Software KaleidaGraph | Systat Software SigmaPlot | The MathWorks MATLAB | UNIX | VMware | Vector Fields OPERA-3d | نرم‌افزار تحلیل ویدیو | Wolfram Research Mathematica | Xfig | xv</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>علوم تجربی | درک مطلب | ریاضیات | تفکر انتقادی | سخن‌گفتن | نگارش | گوش دادن فعال | یادگیری فعال | استراتژی‌های یادگیری | نظارت</t>
+          <t>علوم | درک مطلب | ریاضیات | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>فیزیک | ریاضیات | مهندسی و فناوری | کامپیوتر و الکترونیک | زبان انگلیسی | آموزش و تربیت | شیمی</t>
+          <t>فیزیک | ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | درک کتبی | سهولت کار با اعداد | درک شفاهی | بیان شفاهی | روانی ایده‌ها | خلاقیت | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله | سازماندهی اطلاعات | انعطاف‌پذیری در دسته‌بندی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | تجسم | انعطاف‌پذیری در بستار | سرعت بستار | توجه انتخابی | بینایی دور | سرعت ادراکی</t>
+          <t>استدلال ریاضی | درک کتبی | توانایی عددی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | اصالت | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | تجسم | انعطاف‌پذیری بستار | سرعت بستار | توجه انتخابی | بینایی دور | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان به صورت نشسته | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق بودن یا صحت بالا | فضای بسته، با دمای کنترل‌شده | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی</t>
+          <t>ایمیل | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Aerospace Engineers | Astronomers | Biochemists and Biophysicists | Bioengineers and Biomedical Engineers | Bioinformatics Scientists | Chemical Engineers | Chemists | Computer and Information Research Scientists | Data Scientists | Geoscientists, Except Hydrologists and Geographers | Hydrologists | Materials Scientists | Mathematicians | Microsystems Engineers | Molecular and Cellular Biologists | Nanosystems Engineers | Nanotechnology Engineering Technologists and Technicians | Nuclear Engineers | Physics Teachers, Postsecondary | Statisticians</t>
+          <t>مهندسان هوافضا | اخترشناسان | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | مهندسان شیمی | شیمی‌دانان | دانشمندان تحقیقات کامپیوتر و اطلاعات | دانشمندان داده | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | آب‌شناسان | دانشمندان مواد | ریاضی‌دانان | مهندسان میکروسیستم | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مهندسان هسته‌ای | مدرسان فیزیک، پس از متوسطه | آمارشناسان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AccuWeather Galileo | Adobe Photoshop | Advanced Visual Systems AVS/Express | نرم‌افزار مدل‌سازی کیفیت هوا | Aninoquisi MesoTRAC | Apple Final Cut Pro | Baron Services FasTrac | Baron Volumetric Imaging and Processing of Integrated Radar VIPIR | C++ | Cave5D | Cisco IOS | ESRI ArcInfo | ESRI ArcView | Environmental Research Services RAOB | Facebook | Ferret | Flow Analysis Software Toolkit FAST | Formula translation/translator FORTRAN | Grid analysis and display system GrADS | IBM SPSS Statistics | ITT Visual Information Solutions ENVI | نرم‌افزار ویرایش تصویر | Interactive radar analysis software IRAS | Lakes Environmental Software WRPLOT View | Linux | Maplesoft Maple | نرم‌افزار مدل‌سازی مقیاس متوسط | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Paint | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | PC Weather Products HURRTRAK | Perl | Python | QuarkXPress | R | SAS | STATISTICA | SVRPLOT | SatView | سایت‌های رسانه‌های اجتماعی | ابزارهای توسعه نرم‌افزار | Structured query language SQL | Systat Software SigmaPlot | Systat Software SigmaStat | The MathWorks MATLAB | UNIX | Unidata GEMPAK | Unidata Gempak Analysis and Rendering Program GARP | Unidata Integrated Data Viewer IDV | Unidata McIDAS-X | Vis5d+ | VorTek Site Assessment of Tornado Threat SATT | WINGRIDDS | WSI Titan | WSI TrueView Professional | نرم‌افزار مدل‌سازی جریان باد | Wolfram Research Mathematica</t>
+          <t>AccuWeather Galileo | Adobe Photoshop | Advanced Visual Systems AVS/Express | نرم‌افزار مدل‌سازی کیفیت هوا | Aninoquisi MesoTRAC | Apple Final Cut Pro | Baron Services FasTrac | Baron Volumetric Imaging and Processing of Integrated Radar VIPIR | C++ | Cave5D | Cisco IOS | ESRI ArcInfo | ESRI ArcView | Environmental Research Services RAOB | Facebook | Ferret | Flow Analysis Software Toolkit FAST | Formula translation/translator FORTRAN | Grid analysis and display system GrADS | IBM SPSS Statistics | ITT Visual Information Solutions ENVI | نرم‌افزار ویرایش تصویر | Interactive radar analysis software IRAS | Lakes Environmental Software WRPLOT View | Linux | Maplesoft Maple | نرم‌افزار مدل‌سازی مقیاس متوسط | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Paint | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | PC Weather Products HURRTRAK | Perl | Python | QuarkXPress | R | SAS | STATISTICA | SVRPLOT | SatView | سایت‌های رسانه‌های اجتماعی | ابزارهای توسعه نرم‌افزار | زبان پرس‌وجوی ساختاریافته SQL | Systat Software SigmaPlot | Systat Software SigmaStat | The MathWorks MATLAB | UNIX | Unidata GEMPAK | Unidata Gempak Analysis and Rendering Program GARP | Unidata Integrated Data Viewer IDV | Unidata McIDAS-X | Vis5d+ | VorTek Site Assessment of Tornado Threat SATT | WINGRIDDS | WSI Titan | WSI TrueView Professional | نرم‌افزار مدل‌سازی جریان باد | Wolfram Research Mathematica</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | یادگیری فعال | تفکر انتقادی | علوم تجربی | سخن‌گفتن | گوش دادن فعال | نگارش | ریاضیات | استراتژی‌های یادگیری | نظارت</t>
+          <t>درک مطلب | یادگیری فعال | تفکر انتقادی | علوم | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ریاضیات | فیزیک | جغرافیا | کامپیوتر و الکترونیک | زبان انگلیسی | ارتباطات و رسانه | شیمی | مشتری‌مداری و خدمات شخصی</t>
+          <t>ریاضیات | فیزیک | جغرافیا | رایانه و الکترونیک | زبان انگلیسی | ارتباطات و رسانه | شیمی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | سازماندهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری در بستار | انعطاف‌پذیری در دسته‌بندی | روانی ایده‌ها | خلاقیت | بینایی دور | سهولت کار با اعداد</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | بینایی دور | توانایی عددی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | صرف زمان به صورت نشسته | فضای بسته, با دمای کنترل‌شده | مکالمات تلفنی | آزادی در تصمیم‌گیری | اهمیت دقیق بودن یا صحت بالا | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Astronomers | Climate Change Policy Analysts | Conservation Scientists | Data Scientists | Environmental Scientists and Specialists, Including Health | Geodetic Surveyors | Geographers | Geographic Information Systems Technologists and Technicians | Geological Technicians, Except Hydrologic Technicians | Geoscientists, Except Hydrologists and Geographers | Hydrologic Technicians | Hydrologists | Industrial Ecologists | Physicists | Precision Agriculture Technicians | Remote Sensing Scientists and Technologists | Remote Sensing Technicians | Soil and Plant Scientists | Statisticians | Surveying and Mapping Technicians</t>
+          <t>اخترشناسان | تحلیل‌گران سیاست تغییرات اقلیمی | دانشمندان حفاظت | دانشمندان داده | دانشمندان و متخصصان محیط زیست، شامل بهداشت | نقشه‌برداران ژئودتیک | جغرافیدانان | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | فیزیکدانان | تکنسین‌های کشاورزی دقیق | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | دانشمندان خاک و گیاه | آمارشناسان | تکنسین‌های نقشه‌برداری و نقشه‌کشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Accelrys Cerius2 | Accelrys DeCipher | Advanced Chemistry Development ACD/1D nuclear magnetic resonance NMR processor | Agilent ChemStation | Apple iWork | Apple iWork Keynote | Apple iWork Numbers | Apple iWork Pages | Bruker BioSpin TopSpin | C | C++ | CambridgeSoft ChemOffice Ultra | Chem2Pac | ChemInnovation Software Chem 4-D | ChemSW Buffer Maker | ChemSW Calibration Pro | ChemSW Chemical Inventory System CIS | ChemSW Laboratory Document Control System LDCS | ChemSW Mass Spec Tools | ChemSW Molecular Modeling Pro | ChemSW Uncertainty Pro | نرم‌افزار سینتیک شیمیایی | نرم‌افزار ابزارهای تبدیل | CrystalMaker | نرم‌افزار بلورشناسی | نرم‌افزار نظریه تابعی چگالی DFT | نرم‌افزار تصویربرداری دیجیتال | زبان نشانه گذاری گسترش پذیر XML | نرم‌افزار کروماتوگراف گازی GS | Gaussian software | نرم‌افزار گرافیکی | Hypercube HyperChem | زبان نشانه گذاری ابرمتن HTML | ItemTracker | پایگاه داده JDA Arthur KnowledgeBase | LabTrack Electronic Lab Notebook | Laboratory information management system LIMS | نرم‌افزار ثبت‌کننده داده | MSI Insight/Discover | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | Minitab | نرم‌افزار مدل‌سازی | MolDraw | نرم‌افزار شبیه‌سازی مولکولی | Molsearch Pro | ماشین‌حساب‌های چندمنظوره | National Instruments LabVIEW | NeoOffice | Network Science IR Mentor Pro | Oracle Java | نرم‌افزار برنامه‌ریزی سنتز آلی | Q-Chem | R | نرم‌افزار SAP | SAS JMP | SciQuest PE TurboChrom | Siemens SHELXTL | نرم‌افزار آماری | Structured query language SQL | نرم‌افزار مدل‌سازی سطح | Synthematix StructureSearch | UBI Biotracker | Vogel Scientific Software Group CALACO | Waters Empower Chromatography Data Software | Waters Millennium32 | Wavefunction Spartan</t>
+          <t>Accelrys Cerius2 | Accelrys DeCipher | Advanced Chemistry Development ACD/1D nuclear magnetic resonance NMR processor | Agilent ChemStation | Apple iWork | Apple iWork Keynote | Apple iWork Numbers | Apple iWork Pages | Bruker BioSpin TopSpin | C | C++ | CambridgeSoft ChemOffice Ultra | Chem2Pac | ChemInnovation Software Chem 4-D | ChemSW Buffer Maker | ChemSW Calibration Pro | ChemSW Chemical Inventory System CIS | ChemSW Laboratory Document Control System LDCS | ChemSW Mass Spec Tools | ChemSW Molecular Modeling Pro | ChemSW Uncertainty Pro | نرم‌افزار سینتیک شیمیایی | نرم‌افزار ابزارهای تبدیل | CrystalMaker | نرم‌افزار کریستالوگرافی | نرم‌افزار نظریه تابعی چگالی DFT | نرم‌افزار تصویربرداری دیجیتال | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار کروماتوگراف گازی GS | نرم‌افزار Gaussian | نرم‌افزار گرافیکی | Hypercube HyperChem | زبان نشانه‌گذاری ابرمتن HTML | ItemTracker | پایگاه داده JDA Arthur KnowledgeBase | LabTrack Electronic Lab Notebook | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | نرم‌افزار ثبت‌کننده داده | MSI Insight/Discover | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | Minitab | نرم‌افزار مدل‌سازی | MolDraw | نرم‌افزار شبیه‌سازی مولکولی | Molsearch Pro | ماشین‌حساب‌های چندمنظوره | National Instruments LabVIEW | NeoOffice | Network Science IR Mentor Pro | Oracle Java | نرم‌افزار برنامه‌ریزی سنتز آلی | Q-Chem | R | نرم‌افزار SAP | SAS JMP | SciQuest PE TurboChrom | Siemens SHELXTL | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار مدل‌سازی سطح | Synthematix StructureSearch | UBI Biotracker | Vogel Scientific Software Group CALACO | Waters Empower Chromatography Data Software | Waters Millennium32 | Wavefunction Spartan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>علوم تجربی | تفکر انتقادی | درک مطلب | سخن‌گفتن | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>علوم | تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>شیمی | زبان انگلیسی | ریاضیات | تولید و فرآوری | کامپیوتر و الکترونیک | امور اداری و مدیریت | اداری | فیزیک</t>
+          <t>شیمی | زبان انگلیسی | ریاضیات | تولید و فرآوری | رایانه و الکترونیک | مدیریت و اداره | اداری | فیزیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | سازماندهی اطلاعات | انعطاف‌پذیری در دسته‌بندی | بینایی نزدیک | استدلال ریاضی | سهولت کار با اعداد | انعطاف‌پذیری در بستار | تشخیص گفتار | سرعت ادراکی | وضوح گفتار | تشخیص رنگ‌های بصری | روانی ایده‌ها | ثبات دست و بازو | خلاقیت | زبردستی انگشتان | توجه انتخابی | تجسم</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | استدلال ریاضی | توانایی عددی | انعطاف‌پذیری بستار | تشخیص گفتار | سرعت ادراکی | وضوح گفتار | تشخیص رنگ بصری | روانی ایده‌ها | ثبات دست و بازو | اصالت | مهارت انگشتان | توجه انتخابی | تجسم</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | فضای بسته، با دمای کنترل‌شده | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش, محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | اهمیت دقیق بودن یا صحت بالا | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | مکالمات تلفنی | فشار زمانی | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض شرایط خطرناک | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | مکالمات تلفنی | فشار زمانی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض شرایط خطرناک | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Biochemists and Biophysicists | Bioengineers and Biomedical Engineers | Biological Technicians | Calibration Technologists and Technicians | Chemical Engineers | Chemical Plant and System Operators | Chemical Technicians | Food Science Technicians | Food Scientists and Technologists | Industrial Engineering Technologists and Technicians | Industrial Engineers | Materials Engineers | Materials Scientists | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Microbiologists | Nanosystems Engineers | Nanotechnology Engineering Technologists and Technicians | Natural Sciences Managers | Quality Control Analysts</t>
+          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | تکنسین‌های زیستی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان شیمی | اپراتورهای کارخانه و سامانه‌های شیمیایی | تکنسین‌های شیمی | تکنسین‌های علوم غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان مواد | دانشمندان مواد | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مدیران علوم طبیعی | تحلیل‌گران کنترل کیفیت</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ANSYS LS-DYNA | ANSYS Multiphysics | Accelrys Materials Studio | Advanced Chemistry Development Analytical Laboratory | Bruker AXS EVA | Bruker AXS LEPTOS | Bruker AXS TOPAS | Chempute Software HSC Chemistry | CrystalMaker | Dassault Systemes Abaqus | نرم‌افزار ایمیل | GAMESS-US | General Structural Analysis System GSAS | زبان نشانه گذاری ابرمتن HTML | IBM SPSS Statistics | International Centre for Diffraction Data ICDD DDView | Maplesoft Maple | Materials Data Incorporated Jade | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | نرم‌افزار تحلیلگر میکروالکترود چندکاناله MMA | National Instruments LabVIEW | Olympus Image Analysis | PANalytical X'Pert Data Collector | PANalytical X'Pert Epitaxy | PWscf | Python | R | RIETAN | SolidWorks COSMOSWorks | Stewart Computational Chemistry MOPAC | The MathWorks MATLAB | VAMP/VASP | نرم‌افزار مرورگر وب | Wolfram Research Mathematica</t>
+          <t>ANSYS LS-DYNA | ANSYS Multiphysics | Accelrys Materials Studio | Advanced Chemistry Development Analytical Laboratory | Bruker AXS EVA | Bruker AXS LEPTOS | Bruker AXS TOPAS | Chempute Software HSC Chemistry | CrystalMaker | Dassault Systemes Abaqus | نرم‌افزار ایمیل | GAMESS-US | General Structural Analysis System GSAS | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | International Centre for Diffraction Data ICDD DDView | Maplesoft Maple | Materials Data Incorporated Jade | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | نرم‌افزار تحلیلگر میکروالکترود چندکاناله MMA | National Instruments LabVIEW | Olympus Image Analysis | PANalytical X'Pert Data Collector | PANalytical X'Pert Epitaxy | PWscf | Python | R | RIETAN | SolidWorks COSMOSWorks | Stewart Computational Chemistry MOPAC | The MathWorks MATLAB | VAMP/VASP | نرم‌افزار مرورگر وب | Wolfram Research Mathematica</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم تجربی | گوش دادن فعال | درک مطلب | نگارش | سخن‌گفتن | یادگیری فعال | ریاضیات | نظارت | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | علوم | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | شیمی | فیزیک | ریاضیات | کامپیوتر و الکترونیک | تولید و فرآوری | طراحی | مکانیک | زبان انگلیسی | آموزش و تربیت</t>
+          <t>مهندسی و فناوری | شیمی | فیزیک | ریاضیات | رایانه و الکترونیک | تولید و فرآوری | طراحی | مکانیک | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | سازماندهی اطلاعات | انعطاف‌پذیری در دسته‌بندی | بینایی نزدیک | روانی ایده‌ها | خلاقیت | استدلال ریاضی | انعطاف‌پذیری در بستار | وضوح گفتار | تشخیص گفتار | سهولت کار با اعداد | بینایی دور | تجسم | سرعت ادراکی</t>
+          <t>بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | روانی ایده‌ها | اصالت | استدلال ریاضی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | توانایی عددی | بینایی دور | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | فضای بسته، با دمای کنترل‌شده | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | اهمیت دقیق بودن یا صحت بالا | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان به صورت نشسته | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Bioengineers and Biomedical Engineers | Calibration Technologists and Technicians | Chemical Engineers | Chemical Technicians | Chemists | Electrical Engineers | Electrical and Electronic Engineering Technologists and Technicians | Electronics Engineers, Except Computer | Engineering Teachers, Postsecondary | Industrial Engineering Technologists and Technicians | Industrial Engineers | Manufacturing Engineers | Materials Engineers | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Mechatronics Engineers | Microsystems Engineers | Nanosystems Engineers | Nanotechnology Engineering Technologists and Technicians | Photonics Technicians</t>
+          <t>مهندسان زیستی و مهندسان زیست‌پزشکی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | مدرسان مهندسی، پس از متوسطه | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | مهندسان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ADMS pollution modeling software | Adobe Acrobat | Adobe Illustrator | Autodesk AutoCAD | Bentley MicroStation | C++ | CAP88-PC | CERC EMIT | نرم‌افزار ردیابی مدیریت مواد شیمیایی | Chemicals and Irrigation CANDI | Compass software | Corel CorelDraw Graphics Suite | DQO ELIPGRID-PC | DataPipe EHS | نرم‌افزار پایگاه داده | ESRI ArcGIS software | ESRI ArcInfo | ESRI ArcView | EarthSoft EQuIS Geology | Ecotech WinAQMS | Ecotech WinCollect | نرم‌افزار ردیابی انتشار گازها | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | Golden Software Surfer | نرم‌افزار گرافیکی | Hotspot | IBM SPSS Statistics | Laboratory information management system LIMS | Lakes Environmental EcoRisk View | Lakes Environmental Emissions View | Lakes Environmental ISC-AERMOD View | Lakes Environmental SLAB View | Link Microtek | MIRS Compliance | نرم‌افزار نقشه برداری | نرم‌افزار برگه اطلاعات ایمنی مواد MSDS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint Server | Microsoft Visual Basic | Microsoft Word | RSA RadCalc | Rad Pro Calculator | RockWare ArcMap | نرم‌افزار SAP | Smart Data Solutions RS Solutions | SmugMug Flickr | SoundPLAN | نرم‌افزار آماری | Structured query language SQL | Sun Microsystems Java | TANKS | Tucows ChemBase | نرم‌افزار مرورگر وب | Wolfel IMMI</t>
+          <t>ADMS pollution modeling software | Adobe Acrobat | Adobe Illustrator | Autodesk AutoCAD | Bentley MicroStation | C++ | CAP88-PC | CERC EMIT | نرم‌افزار ردیابی مدیریت مواد شیمیایی | Chemicals and Irrigation CANDI | Compass software | Corel CorelDraw Graphics Suite | DQO ELIPGRID-PC | DataPipe EHS | نرم‌افزار پایگاه داده | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | ESRI ArcView | EarthSoft EQuIS Geology | Ecotech WinAQMS | Ecotech WinCollect | نرم‌افزار ردیابی انتشار گازها | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | Golden Software Surfer | نرم‌افزار گرافیکی | Hotspot | IBM SPSS Statistics | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Lakes Environmental EcoRisk View | Lakes Environmental Emissions View | Lakes Environmental ISC-AERMOD View | Lakes Environmental SLAB View | Link Microtek | MIRS Compliance | نرم‌افزار نقشه‌برداری | نرم‌افزار برگه اطلاعات ایمنی مواد MSDS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint Server | Microsoft Visual Basic | Microsoft Word | RSA RadCalc | Rad Pro Calculator | RockWare ArcMap | نرم‌افزار SAP | Smart Data Solutions RS Solutions | SmugMug Flickr | SoundPLAN | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java | TANKS | Tucows ChemBase | نرم‌افزار مرورگر وب | Wolfel IMMI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم تجربی | سخن‌گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | علوم | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | زیست‌شناسی | مشتری‌مداری و خدمات شخصی | قوانین و مقررات دولتی | کامپیوتر و الکترونیک | امنیت و ایمنی عمومی | شیمی | اداری | ریاضیات | آموزش و تربیت | امور اداری و مدیریت</t>
+          <t>زبان انگلیسی | زیست‌شناسی | خدمات مشتری و شخصی | قانون و دولت | رایانه و الکترونیک | ایمنی و امنیت عمومی | شیمی | اداری | ریاضیات | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | بیان کتبی | استدلال استقرایی | سازماندهی اطلاعات | انعطاف‌پذیری در دسته‌بندی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری در بستار | استدلال ریاضی | خلاقیت | روانی ایده‌ها | بینایی دور | سهولت کار با اعداد</t>
+          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری بستار | استدلال ریاضی | اصالت | روانی ایده‌ها | بینایی دور | توانایی عددی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | صرف زمان به صورت نشسته | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق بودن یا صحت بالا | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | فضای بسته، با دمای کنترل‌شده</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Brownfield Redevelopment Specialists and Site Managers | Chief Sustainability Officers | Climate Change Policy Analysts | Conservation Scientists | Environmental Compliance Inspectors | Environmental Engineering Technologists and Technicians | Environmental Engineers | Environmental Restoration Planners | Environmental Science Teachers, Postsecondary | Environmental Science and Protection Technicians, Including Health | Foresters | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Hydrologic Technicians | Hydrologists | Industrial Ecologists | Occupational Health and Safety Specialists | Occupational Health and Safety Technicians | Range Managers | Soil and Plant Scientists | Water Resource Specialists</t>
+          <t>متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | تحلیل‌گران سیاست تغییرات اقلیمی | دانشمندان حفاظت | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | مدرسان علوم محیطی، پس از متوسطه | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | جنگل‌بانان | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | مدیران مراتع | دانشمندان خاک و گیاه | متخصصان منابع آب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0023_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0023_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | زیست‌شناسی | حقوق و امور دولتی | ریاضیات | جغرافیا | ایمنی و امنیت عمومی | آموزش و تدریس | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | زیست‌شناسی | قانون و دولت | ریاضیات | جغرافیا | ایمنی و امنیت عمومی | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | حساسیت به مسئله | بیان کتبی | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری در ادراک الگو | اصالت و نوآوری | دید دور | استحکام تنه | تجسم | روانی ایده‌ها | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | اصالت | بینایی دور | قدرت تنه | تجسم | روانی ایده‌ها | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | متخصصان و مدیران احیای اراضی بایر | مدیران ارشد پایداری | کارشناسان حفاظت از منابع طبیعی | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | کاردان‌ها و تکنسین‌های علوم محیطی و حفاظت (شامل بهداشت) | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | چوب‌بُرها | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | بازرسان و کارشناسان پیشگیری از آتش‌سوزی جنگل | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | کارگران جنگل‌داری و حفاظت | کارشناسان هیدرولوژی و آب‌شناسی | کارشناسان بوم‌شناسی صنعتی | تکنسین‌های کشاورزی دقیق | کارشناسان مدیریت مرتع | متخصصان علوم خاک و گیاه‌شناسی | متخصصان منابع آب | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>مهندسان کشاورزی | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران ارشد پایداری سازمانی | دانشمندان حفاظت از منابع طبیعی | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | درخت‌اندازان و چوب‌بُران جنگل | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | بازرسان و کارشناسان پیشگیری از حریق جنگل | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | تکنسین‌های کشاورزی دقیق | مدیران و کارشناسان مدیریت مراتع | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان و متخصصان مدیریت منابع آب | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | علوم تجربی | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | علوم | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ریاضیات | زیست‌شناسی | زبان انگلیسی | پزشکی و دندانپزشکی | رایانه و الکترونیک | ارتباطات و رسانه | آموزش و تدریس | جامعه‌شناسی و مردم‌شناسی | مدیریت و امور اداری</t>
+          <t>ریاضیات | زیست‌شناسی | زبان انگلیسی | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | ارتباطات و رسانه | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | روانی ایده‌ها | اصالت و نوآوری | دید نزدیک | مرتب‌سازی اطلاعات | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری در ادراک الگو | مهارت محاسباتی | توجه انتخابی | تجسم | سرعت ادراک | سرعت در درک الگو</t>
+          <t>درک شفاهی | درک کتبی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | روانی ایده‌ها | اصالت | بینایی نزدیک | ترتیب‌دهی اطلاعات | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی | توجه انتخابی | تجسم | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان قلب و عروق | متخصصان روان‌شناسی بالینی اعصاب | کارشناسان ارشد پرستاری بالینی | هماهنگ‌کنندگان پژوهش‌های بالینی | متخصصان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | مشاوران ژنتیک | متخصصان ژنتیک | کارشناسان آموزش بهداشت | کارشناسان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | مدرسان رشته‌های علوم پزشکی در دانشگاه‌ها | دانشمندان علوم پزشکی (به‌جز همه‌گیرشناسان) | میکروب‌شناسان | متخصصان نوروسایکولوژی | پرستاران دوره‌دیده مراقبت‌های اولیه | جراحان اطفال | پزشکان متخصص آسیب‌شناسی (پاتولوژیست‌ها) | متخصصان پزشکی اجتماعی و پیشگیری</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیماری‌های قلب و عروق | متخصصان عصب‌روان‌شناسی بالینی | پرستاران متخصص بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | مشاوران ژنتیک | متخصصان ژنتیک | کارشناسان آموزش بهداشت و ارتقای سلامت | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | پژوهشگران و دانشمندان علوم پزشکی | میکروبیولوژیست‌ها | متخصصان عصب‌روان‌شناسی | پرستاران بالینی پیشرفته | جراحان اطفال | پزشکان متخصص پاتولوژی | متخصصان پزشکی اجتماعی و طب پیشگیری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نگارش | علوم تجربی | یادگیری فعال | سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>نگارش | علوم | یادگیری فعال | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | پزشکی و دندانپزشکی | شیمی | ریاضیات</t>
+          <t>زیست‌شناسی | زبان انگلیسی | پزشکی و دندان‌پزشکی | شیمی | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | درک شفاهی | درک کتبی | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | استدلال ریاضی | روانی ایده‌ها | اصالت و نوآوری | انعطاف‌پذیری در ادراک الگو | مهارت محاسباتی | توجه انتخابی | سرعت در درک الگو | حافظه و به‌خاطرسپاری | سرعت ادراک</t>
+          <t>بیان شفاهی | بیان کتبی | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک شفاهی | درک کتبی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | توانایی عددی | توجه انتخابی | سرعت بستار | حفظ کردن | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان بیوالکتریک و مهندسان پزشکی | متخصصان بیوانفورماتیک | تکنسین‌های آزمایشگاه زیستی | متخصصان قلب و عروق | متخصصان روان‌شناسی بالینی اعصاب | هماهنگ‌کنندگان پژوهش‌های بالینی | تکنسین‌های سیتوژنتیک | همه‌گیرشناسان | متخصصان ژنتیک | تکنسین‌های بافت‌شناسی | کاردان‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | میکروب‌شناسان | زیست‌شناسان مولکولی و سلولی | جراحان اطفال | پزشکان متخصص آسیب‌شناسی (پاتولوژیست‌ها) | متخصصان پزشکی اجتماعی و پیشگیری | متخصصان رادیولوژی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های علوم زیستی | متخصصان بیماری‌های قلب و عروق | متخصصان عصب‌روان‌شناسی بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | کارشناسان سیتوژنتیک | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | متخصصان ژنتیک | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | جراحان اطفال | پزشکان متخصص پاتولوژی | متخصصان پزشکی اجتماعی و طب پیشگیری | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم تجربی | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | پزشکی و دندانپزشکی | رایانه و الکترونیک | آموزش و تدریس | مدیریت و امور اداری | فیزیک</t>
+          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | آموزش و پرورش | مدیریت و اداره | فیزیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | اصالت و نوآوری | توجه انتخابی | تسهیم زمان | تجسم | حافظه و به‌خاطرسپاری | استدلال ریاضی | مهارت محاسباتی | سرعت ادراک | انعطاف‌پذیری در ادراک الگو</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>زیست‌شناسان | میکروب‌شناسان | بیوشیمی‌دانان و بیوفیزیک‌دانان | زیست‌شناسان مولکولی و سلولی | متخصصان ژنتیک | متخصصان بیوانفورماتیک | دانشمندان علوم پزشکی (به‌جز همه‌گیرشناسان) | همه‌گیرشناسان | جانورشناسان و زیست‌شناسان حیات وحش | متخصصان علوم دامی | متخصصان علوم خاک و گیاه‌شناسی | دانشمندان و کارشناسان صنایع غذایی | کارشناسان حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | تکنسین‌های آزمایشگاه زیستی | مدیران علوم طبیعی | مدرسان علوم زیستی در دانشگاه‌ها | مدرسان رشته‌های علوم پزشکی در دانشگاه‌ها | هماهنگ‌کنندگان پژوهش‌های بالینی</t>
+          <t>زیست‌شناسان | میکروبیولوژیست‌ها | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | زیست‌شناسان سلولی و مولکولی | متخصصان ژنتیک | متخصصان بیوانفورماتیک | پژوهشگران و دانشمندان علوم پزشکی | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | جانورشناسان و زیست‌شناسان حیات وحش | متخصصان علوم دامی | متخصصان خاک‌شناسی و علوم گیاهی | متخصصان و کارشناسان علوم و صنایع غذایی | دانشمندان حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | تکنسین‌های علوم زیستی | مدیران علوم طبیعی و پایه‌ای | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | هماهنگ‌کنندگان کارآزمایی‌های بالینی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم تجربی | نگارش | ریاضیات | تفکر انتقادی | شنیدن فعال | یادگیری فعال | سخن گفتن | راهبردهای یادگیری | نظارت</t>
+          <t>درک مطلب | علوم | نگارش | ریاضیات | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | سخن گفتن | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>فیزیک | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | آموزش و تدریس | مهندسی و فناوری | شیمی</t>
+          <t>فیزیک | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | مهندسی و فناوری | شیمی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | مهارت محاسباتی | وضوح گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در ادراک الگو | دید نزدیک | دید دور | روانی ایده‌ها | اصالت و نوآوری | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | تشخیص گفتار | سرعت ادراک | تشخیص رنگ‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | توانایی عددی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی نزدیک | بینایی دور | روانی ایده‌ها | اصالت | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تشخیص گفتار | سرعت ادراکی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دانشمندان علوم جوی و فضا | مدرسان علوم جوی، زمین‌شناسی، علوم دریایی و فضایی در دانشگاه‌ها | بیوشیمی‌دانان و بیوفیزیک‌دانان | متخصصان بیوانفورماتیک | زیست‌شناسان | شیمی‌دانان | دانشمندان علوم رایانه و پژوهشگران فناوری اطلاعات | دانشمندان داده | مدرسان رشته‌های مهندسی در دانشگاه‌ها | مدرسان علوم محیطی در دانشگاه‌ها | کارشناسان علوم زمین (به‌جز آب‌شناسان و جغرافیدانان) | کارشناسان هیدرولوژی و آب‌شناسی | مدرسان علوم ریاضی در دانشگاه‌ها | ریاضی‌دانان | زیست‌شناسان مولکولی و سلولی | مهندسان سامانه‌های نانو | کارشناسان و تکنسین‌های مهندسی فناوری نانو | فیزیک‌دانان | مدرسان فیزیک در دانشگاه‌ها | آمارشناسان</t>
+          <t>دانشمندان و کارشناسان علوم جوی و فضا | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | متخصصان بیوانفورماتیک | زیست‌شناسان | شیمی‌دانان | پژوهشگران علوم رایانه و اطلاعات | دانشمندان داده | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | ریاضی‌دانان | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | فیزیک‌دانان | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>علوم تجربی | درک مطلب | ریاضیات | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>علوم | درک مطلب | ریاضیات | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>فیزیک | ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | آموزش و تدریس | شیمی</t>
+          <t>فیزیک | ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | درک کتبی | مهارت محاسباتی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | اصالت و نوآوری | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | تشخیص گفتار | وضوح گفتار | دید نزدیک | تجسم | انعطاف‌پذیری در ادراک الگو | سرعت در درک الگو | توجه انتخابی | دید دور | سرعت ادراک</t>
+          <t>استدلال ریاضی | درک کتبی | توانایی عددی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | اصالت | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | تجسم | انعطاف‌پذیری بستار | سرعت بستار | توجه انتخابی | بینایی دور | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان هوافضا | ستاره‌شناسان و اخترشناسان | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان بیوالکتریک و مهندسان پزشکی | متخصصان بیوانفورماتیک | مهندسان شیمی | شیمی‌دانان | دانشمندان علوم رایانه و پژوهشگران فناوری اطلاعات | دانشمندان داده | کارشناسان علوم زمین (به‌جز آب‌شناسان و جغرافیدانان) | کارشناسان هیدرولوژی و آب‌شناسی | کارشناسان علوم مواد | ریاضی‌دانان | مهندسان میکروسیستم | زیست‌شناسان مولکولی و سلولی | مهندسان سامانه‌های نانو | کارشناسان و تکنسین‌های مهندسی فناوری نانو | مهندسان هسته‌ای | مدرسان فیزیک در دانشگاه‌ها | آمارشناسان</t>
+          <t>مهندسان هوافضا | ستاره‌شناسان و اخترشناسان | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | مهندسان شیمی | شیمی‌دانان | پژوهشگران علوم رایانه و اطلاعات | دانشمندان داده | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | کارشناسان و دانشمندان علوم مواد | ریاضی‌دانان | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مهندسان هسته‌ای | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | یادگیری فعال | تفکر انتقادی | علوم تجربی | سخن گفتن | شنیدن فعال | نگارش | ریاضیات | راهبردهای یادگیری | نظارت</t>
+          <t>درک مطلب | یادگیری فعال | تفکر انتقادی | علوم | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ریاضیات | فیزیک | جغرافیا | رایانه و الکترونیک | زبان انگلیسی | ارتباطات و رسانه | شیمی | خدمات مشتریان و خدمات فردی</t>
+          <t>ریاضیات | فیزیک | جغرافیا | رایانه و الکترونیک | زبان انگلیسی | ارتباطات و رسانه | شیمی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | استدلال ریاضی | انعطاف‌پذیری در ادراک الگو | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | اصالت و نوآوری | دید دور | مهارت محاسباتی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | بینایی دور | توانایی عددی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ستاره‌شناسان و اخترشناسان | تحلیل‌گران سیاست‌های تغییرات اقلیمی | کارشناسان حفاظت از منابع طبیعی | دانشمندان داده | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | نقشه‌برداران ژئودزی | جغرافیدانان | کارشناسان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی GIS | تکنسین‌های زمین‌شناسی (به‌جز تکنسین‌های آب‌شناسی) | کارشناسان علوم زمین (به‌جز آب‌شناسان و جغرافیدانان) | تکنسین‌های هیدرولوژی | کارشناسان هیدرولوژی و آب‌شناسی | کارشناسان بوم‌شناسی صنعتی | فیزیک‌دانان | تکنسین‌های کشاورزی دقیق | کارشناسان و متخصصان سنجش از دور | تکنسین‌های سنجش از دور | متخصصان علوم خاک و گیاه‌شناسی | آمارشناسان | تکنسین‌های نقشه‌برداری</t>
+          <t>ستاره‌شناسان و اخترشناسان | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | دانشمندان داده | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مهندسان نقشه‌برداری ژئودزی | جغرافیدانان | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | فیزیک‌دانان | تکنسین‌های کشاورزی دقیق | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان آمار | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>علوم تجربی | تفکر انتقادی | درک مطلب | سخن گفتن | شنیدن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>علوم | تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>شیمی | زبان انگلیسی | ریاضیات | تولید و فرآوری | رایانه و الکترونیک | مدیریت و امور اداری | امور اداری و دفتری | فیزیک</t>
+          <t>شیمی | زبان انگلیسی | ریاضیات | تولید و فرآوری | رایانه و الکترونیک | مدیریت و اداره | اداری | فیزیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | استدلال ریاضی | مهارت محاسباتی | انعطاف‌پذیری در ادراک الگو | تشخیص گفتار | سرعت ادراک | وضوح گفتار | تشخیص رنگ‌ها | روانی ایده‌ها | ثبات دست و بازو | اصالت و نوآوری | چابکی انگشتان | توجه انتخابی | تجسم</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | استدلال ریاضی | توانایی عددی | انعطاف‌پذیری بستار | تشخیص گفتار | سرعت ادراکی | وضوح گفتار | تشخیص رنگ بصری | روانی ایده‌ها | ثبات دست و بازو | اصالت | مهارت انگشتان | توجه انتخابی | تجسم</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان بیوالکتریک و مهندسان پزشکی | تکنسین‌های آزمایشگاه زیستی | کارشناسان و تکنسین‌های کالیبراسیون | مهندسان شیمی | متصدیان و بهره‌برداران فرآیند در صنایع شیمیایی | تکنسین‌های شیمی | تکنسین‌های علوم و صنایع غذایی | دانشمندان و کارشناسان صنایع غذایی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان مواد | کارشناسان علوم مواد | کاردان‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | میکروب‌شناسان | مهندسان سامانه‌های نانو | کارشناسان و تکنسین‌های مهندسی فناوری نانو | مدیران علوم طبیعی | کارشناسان تحلیل و کنترل کیفیت</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | تکنسین‌های علوم زیستی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان شیمی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | تکنسین‌های شیمی | تکنسین‌های علوم و صنایع غذایی | متخصصان و کارشناسان علوم و صنایع غذایی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان متالورژی و مواد | کارشناسان و دانشمندان علوم مواد | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مدیران علوم طبیعی و پایه‌ای | کارشناسان تحلیل کنترل کیفیت</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم تجربی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | علوم | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | شیمی | فیزیک | ریاضیات | رایانه و الکترونیک | تولید و فرآوری | طراحی | مکانیک | زبان انگلیسی | آموزش و تدریس</t>
+          <t>مهندسی و فناوری | شیمی | فیزیک | ریاضیات | رایانه و الکترونیک | تولید و فرآوری | طراحی | مکانیک | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | روانی ایده‌ها | اصالت و نوآوری | استدلال ریاضی | انعطاف‌پذیری در ادراک الگو | وضوح گفتار | تشخیص گفتار | مهارت محاسباتی | دید دور | تجسم | سرعت ادراک</t>
+          <t>بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | روانی ایده‌ها | اصالت | استدلال ریاضی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | توانایی عددی | بینایی دور | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان بیوالکتریک و مهندسان پزشکی | کارشناسان و تکنسین‌های کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک (به‌جز رایانه) | مدرسان رشته‌های مهندسی در دانشگاه‌ها | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان ساخت و تولید | مهندسان مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان سامانه‌های نانو | کارشناسان و تکنسین‌های مهندسی فناوری نانو | تکنسین‌های فوتونیک</t>
+          <t>مهندسان پزشکی و بیوانجینیرینگ | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان متالورژی و مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک و اپتیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم تجربی | سخن گفتن | نگارش | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | علوم | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | حقوق و امور دولتی | رایانه و الکترونیک | ایمنی و امنیت عمومی | شیمی | امور اداری و دفتری | ریاضیات | آموزش و تدریس | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | زیست‌شناسی | خدمات مشتری و شخصی | قانون و دولت | رایانه و الکترونیک | ایمنی و امنیت عمومی | شیمی | اداری | ریاضیات | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | بیان کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | تشخیص گفتار | وضوح گفتار | دید نزدیک | انعطاف‌پذیری در ادراک الگو | استدلال ریاضی | اصالت و نوآوری | روانی ایده‌ها | دید دور | مهارت محاسباتی</t>
+          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری بستار | استدلال ریاضی | اصالت | روانی ایده‌ها | بینایی دور | توانایی عددی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان و مدیران احیای اراضی بایر | مدیران ارشد پایداری | تحلیل‌گران سیاست‌های تغییرات اقلیمی | کارشناسان حفاظت از منابع طبیعی | بازرسان انطباق محیط‌زیستی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | مدرسان علوم محیطی در دانشگاه‌ها | کاردان‌ها و تکنسین‌های علوم محیطی و حفاظت (شامل بهداشت) | کارشناسان جنگل‌داری و جنگل‌بانان | مهندسان بهداشت و ایمنی (به‌جز مهندسان و بازرسان ایمنی معدن) | تکنسین‌های هیدرولوژی | کارشناسان هیدرولوژی و آب‌شناسی | کارشناسان بوم‌شناسی صنعتی | کارشناسان بهداشت و ایمنی حرفه‌ای | تکنسین‌های بهداشت و ایمنی حرفه‌ای | کارشناسان مدیریت مرتع | متخصصان علوم خاک و گیاه‌شناسی | متخصصان منابع آب</t>
+          <t>مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران ارشد پایداری سازمانی | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان جنگل‌داری و جنگل‌بانان | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | مدیران و کارشناسان مدیریت مراتع | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان و متخصصان مدیریت منابع آب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
